--- a/accountant-skill/data/output/Aug2025/audit_validation_Aug2025.xlsx
+++ b/accountant-skill/data/output/Aug2025/audit_validation_Aug2025.xlsx
@@ -558,7 +558,7 @@
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>2025-08-01 to 2025-08-31</t>
+          <t>2025-Aug-01 to 2025-Aug-31</t>
         </is>
       </c>
     </row>
@@ -728,7 +728,7 @@
       </c>
       <c r="D18" s="12" t="inlineStr">
         <is>
-          <t>Assets=1,014,233,968.76, Equity=1,014,233,968.76, Liabilities=0.00, Diff=0.00</t>
+          <t>Assets=1,453,764,791.76, Equity=1,453,764,791.76, Liabilities=0.00, Diff=0.00</t>
         </is>
       </c>
       <c r="E18" s="12" t="inlineStr"/>
@@ -785,7 +785,7 @@
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>2025-08-01 to 2025-08-31</t>
+          <t>2025-Aug-01 to 2025-Aug-31</t>
         </is>
       </c>
     </row>
@@ -820,7 +820,7 @@
       </c>
       <c r="C6" s="12" t="inlineStr">
         <is>
-          <t>Assets=1,014,233,968.76, Equity=1,014,233,968.76, Liabilities=0.00, Diff=0.00</t>
+          <t>Assets=1,453,764,791.76, Equity=1,453,764,791.76, Liabilities=0.00, Diff=0.00</t>
         </is>
       </c>
     </row>
